--- a/HSI_FSC_result/5. KshotNquery/result_kshotnquery_parameters.xlsx
+++ b/HSI_FSC_result/5. KshotNquery/result_kshotnquery_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\5. KshotNquery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD194945-FF00-4C79-BE0B-A0E9014532CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C14F908-986E-4618-93AD-C152A3F42829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="62">
   <si>
     <t>murphy</t>
   </si>
@@ -205,10 +205,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>30way</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5+15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -222,6 +218,18 @@
   </si>
   <si>
     <t>1+19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Indian Pines</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>University of Pavia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salinas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -229,9 +237,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -293,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -367,6 +376,10 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3792,16 +3805,16 @@
       <c r="A1" s="14"/>
       <c r="B1" s="14"/>
       <c r="D1" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>57</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="H1" s="17"/>
       <c r="I1" s="15"/>
@@ -4187,16 +4200,16 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="E29" s="15" t="s">
         <v>57</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -4281,21 +4294,19 @@
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" s="3"/>
       <c r="D1" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="15" t="s">
-        <v>58</v>
-      </c>
       <c r="H1" s="4"/>
-      <c r="I1" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -4315,9 +4326,7 @@
         <v>85.977138999999994</v>
       </c>
       <c r="H2" s="21"/>
-      <c r="I2" s="21">
-        <v>88.840453600000004</v>
-      </c>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -4337,9 +4346,7 @@
         <v>94.291404499999999</v>
       </c>
       <c r="H3" s="22"/>
-      <c r="I3" s="22">
-        <v>92.563658500000003</v>
-      </c>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -4359,9 +4366,7 @@
         <v>61.936311699999997</v>
       </c>
       <c r="H4" s="22"/>
-      <c r="I4" s="22">
-        <v>51.713974499999999</v>
-      </c>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -4381,9 +4386,7 @@
         <v>70.854438299999998</v>
       </c>
       <c r="H5" s="22"/>
-      <c r="I5" s="22">
-        <v>82.242330199999998</v>
-      </c>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -4403,9 +4406,7 @@
         <v>93.470371099999994</v>
       </c>
       <c r="H6" s="22"/>
-      <c r="I6" s="22">
-        <v>91.793442200000001</v>
-      </c>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -4425,9 +4426,7 @@
         <v>41.521521100000001</v>
       </c>
       <c r="H7" s="22"/>
-      <c r="I7" s="22">
-        <v>37.915383200000001</v>
-      </c>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -4447,9 +4446,7 @@
         <v>53.564862099999999</v>
       </c>
       <c r="H8" s="22"/>
-      <c r="I8" s="22">
-        <v>66.9356583</v>
-      </c>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -4469,9 +4466,7 @@
         <v>70.573956800000005</v>
       </c>
       <c r="H9" s="22"/>
-      <c r="I9" s="22">
-        <v>72.616423400000002</v>
-      </c>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -4491,9 +4486,7 @@
         <v>66.374058300000002</v>
       </c>
       <c r="H10" s="22"/>
-      <c r="I10" s="22">
-        <v>70.241495700000002</v>
-      </c>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
@@ -4514,9 +4507,7 @@
         <v>70.880400219999999</v>
       </c>
       <c r="H11" s="23"/>
-      <c r="I11" s="23">
-        <v>71.861090329999996</v>
-      </c>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
@@ -4537,9 +4528,7 @@
         <v>70.951562519999996</v>
       </c>
       <c r="H12" s="23"/>
-      <c r="I12" s="23">
-        <v>72.762534619999997</v>
-      </c>
+      <c r="I12" s="23"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
@@ -4560,22 +4549,20 @@
         <v>64.309848270000003</v>
       </c>
       <c r="H13" s="23"/>
-      <c r="I13" s="23">
-        <v>64.815161200000006</v>
-      </c>
+      <c r="I13" s="23"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B17" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="E17" s="15" t="s">
         <v>57</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="3"/>
@@ -4647,7 +4634,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339BABA6-06F5-45C7-A2FD-80F82689477E}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="1"/>
@@ -4658,16 +4645,16 @@
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="D1" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>57</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="H1" s="16"/>
       <c r="I1" s="14"/>
@@ -5124,16 +5111,16 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B28" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="E28" s="15" t="s">
         <v>57</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="14"/>
@@ -5194,6 +5181,202 @@
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="18"/>
+    </row>
+    <row r="38" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="K38" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38" t="s">
+        <v>55</v>
+      </c>
+      <c r="M38" t="s">
+        <v>56</v>
+      </c>
+      <c r="N38" t="s">
+        <v>57</v>
+      </c>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+    </row>
+    <row r="39" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I39" t="s">
+        <v>59</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1</v>
+      </c>
+      <c r="K39" s="30">
+        <v>53.724088379999998</v>
+      </c>
+      <c r="L39" s="30">
+        <v>52.916382089999999</v>
+      </c>
+      <c r="M39" s="30">
+        <v>50.232217779999999</v>
+      </c>
+      <c r="N39" s="30">
+        <v>55.461020589999997</v>
+      </c>
+      <c r="O39" s="14"/>
+      <c r="P39" s="14"/>
+    </row>
+    <row r="40" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="J40" t="s">
+        <v>2</v>
+      </c>
+      <c r="K40" s="30">
+        <v>52.591433850000001</v>
+      </c>
+      <c r="L40" s="30">
+        <v>50.709094999999998</v>
+      </c>
+      <c r="M40" s="30">
+        <v>50.102676449999997</v>
+      </c>
+      <c r="N40" s="30">
+        <v>53.99969548</v>
+      </c>
+      <c r="O40" s="14"/>
+      <c r="P40" s="14"/>
+    </row>
+    <row r="41" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="J41" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="30">
+        <v>48.784211839999998</v>
+      </c>
+      <c r="L41" s="30">
+        <v>47.888372420000003</v>
+      </c>
+      <c r="M41" s="30">
+        <v>45.051149860000002</v>
+      </c>
+      <c r="N41" s="30">
+        <v>50.441960459999997</v>
+      </c>
+      <c r="O41" s="14"/>
+      <c r="P41" s="14"/>
+    </row>
+    <row r="42" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I42" t="s">
+        <v>60</v>
+      </c>
+      <c r="J42" t="s">
+        <v>1</v>
+      </c>
+      <c r="K42" s="30">
+        <v>73.654300629999994</v>
+      </c>
+      <c r="L42" s="30">
+        <v>71.537310640000001</v>
+      </c>
+      <c r="M42" s="30">
+        <v>72.273938659999999</v>
+      </c>
+      <c r="N42" s="30">
+        <v>70.880400219999999</v>
+      </c>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+    </row>
+    <row r="43" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="J43" t="s">
+        <v>2</v>
+      </c>
+      <c r="K43" s="30">
+        <v>71.89961022</v>
+      </c>
+      <c r="L43" s="30">
+        <v>70.108795169999993</v>
+      </c>
+      <c r="M43" s="30">
+        <v>71.779994369999997</v>
+      </c>
+      <c r="N43" s="30">
+        <v>70.951562519999996</v>
+      </c>
+      <c r="O43" s="22"/>
+      <c r="P43" s="22"/>
+    </row>
+    <row r="44" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="J44" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="30">
+        <v>66.739814120000005</v>
+      </c>
+      <c r="L44" s="30">
+        <v>64.288613679999997</v>
+      </c>
+      <c r="M44" s="30">
+        <v>65.248609200000004</v>
+      </c>
+      <c r="N44" s="30">
+        <v>64.309848270000003</v>
+      </c>
+      <c r="O44" s="22"/>
+      <c r="P44" s="22"/>
+    </row>
+    <row r="45" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I45" t="s">
+        <v>61</v>
+      </c>
+      <c r="J45" t="s">
+        <v>1</v>
+      </c>
+      <c r="K45" s="30">
+        <v>86.866727460000007</v>
+      </c>
+      <c r="L45" s="30">
+        <v>86.727447389999995</v>
+      </c>
+      <c r="M45" s="30">
+        <v>85.262798129999993</v>
+      </c>
+      <c r="N45" s="30">
+        <v>85.962238360000001</v>
+      </c>
+      <c r="O45" s="14"/>
+      <c r="P45" s="14"/>
+    </row>
+    <row r="46" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="J46" t="s">
+        <v>2</v>
+      </c>
+      <c r="K46" s="30">
+        <v>90.425407340000007</v>
+      </c>
+      <c r="L46" s="30">
+        <v>90.147847530000007</v>
+      </c>
+      <c r="M46" s="30">
+        <v>87.670387629999993</v>
+      </c>
+      <c r="N46" s="30">
+        <v>89.446362260000001</v>
+      </c>
+      <c r="O46" s="14"/>
+      <c r="P46" s="14"/>
+    </row>
+    <row r="47" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="J47" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="30">
+        <v>85.43888647</v>
+      </c>
+      <c r="L47" s="30">
+        <v>85.30082444</v>
+      </c>
+      <c r="M47" s="30">
+        <v>83.699148539999996</v>
+      </c>
+      <c r="N47" s="30">
+        <v>84.447265610000002</v>
+      </c>
+      <c r="O47" s="14"/>
+      <c r="P47" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
